--- a/Feuilles/Histoire A.xlsx
+++ b/Feuilles/Histoire A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B6D9E1-56A0-564C-89EF-C117C0663322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20C27E-A52A-344B-879A-AEBFA74B75DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17140" yWindow="2800" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="6660" yWindow="2820" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>MES</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>OUTRO</t>
+  </si>
+  <si>
+    <t>LOOP</t>
+  </si>
+  <si>
+    <t>COUPLET 3bis</t>
   </si>
 </sst>
 </file>
@@ -452,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,8 +474,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -483,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -494,7 +503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -505,7 +514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -516,7 +525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -527,7 +536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -538,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -549,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -560,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -574,7 +583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -585,7 +594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -596,7 +605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -607,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -618,7 +627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -629,7 +638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -891,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">

--- a/Feuilles/Histoire A.xlsx
+++ b/Feuilles/Histoire A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20C27E-A52A-344B-879A-AEBFA74B75DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425E798-7A61-E44E-8F8D-85DF998DB53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6660" yWindow="2820" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1073,8 +1073,11 @@
       <c r="D53" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1107,7 +1110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1118,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1142,8 +1145,11 @@
       <c r="D59" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1165,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1190,7 +1196,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
